--- a/datasets/数据集清单.xlsx
+++ b/datasets/数据集清单.xlsx
@@ -13,6 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'实测数据'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推理与交互'!$A$4:$I$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'推理与交互'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -618,7 +619,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>已全量核对；当前实验来源</t>
+          <t>已全量核对；已归档表格候选的实验来源</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -665,7 +666,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>已全量核对；当前实验溯源</t>
+          <t>已全量核对；已归档表格候选的溯源</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -756,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -773,14 +774,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>推理与交互清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+          <t>文献、推理与实验方案数据清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>按已有来源核验记录整理（2026-10-09）。规模来源与实际取样范围分别标明；地址以公开原入口为准。</t>
+          <t>供候选问题筛选；未指定为研究路线。论文规模、公开子集与实际核验范围分别标明。更新：2026-10-09。</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2148,102 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="120" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>BioProt / BioPlanner</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>实验协议</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/bioplanner/bioplanner</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>论文整理 100 个生物协议，平均 12.5 步；有原文、函数定义和伪代码。</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>GPT-4 转写后经实验人员逐行核对；不是全量协议执行成功标签。</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>已核论文构造方法及官方仓库入口；未逐行审计全部数据。</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>候选 03：步骤顺序、参数完整性、协议重建的基础对照。</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>函数集合来自完整协议，提供强先验；伪代码相似不保证真实可执行，等价操作可能被错判。</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09；arXiv:2310.10632v1；GitHub API 未识别统一许可，原协议和派生内容许可需分别核实。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>LAB-Bench（含 ProtocolQA）</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>生物研究与协议修复</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/futurehouse/lab-bench</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>论文全套 2,457 题、ProtocolQA 135 题；当前公开数据卡为 1,967 题，其中 ProtocolQA 108 题。</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>选择题答案与干扰项；协议子任务由专家注错、核验影响并构造修复题。</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>已核原论文方法与官方数据卡；未下载全量题目、未复核逐题标签。</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>候选 03：协议错误诊断与修复选择；文献、表格等子任务可作局部评价。</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>公开子集不等于完整评测；选择题可利用排除法，正确选项不证明修复后可实施；train 字段不代表已按来源隔离训练与确认样本。</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09；数据卡 CC BY-SA 4.0；arXiv:2407.10362v3；本次数据版本 5c77cec648430f30611808808861eb86f81d5eaa。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:I34"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -2181,12 +2277,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId30"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId29"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2197,7 +2295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2212,15 +2310,15 @@
       </c>
       <c r="B1" s="7" t="inlineStr"/>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>当前实验</t>
+          <t>已归档候选</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>Buchwald–Hartwig 与 Doyle CN 是同一实验来源，不能当作两个独立来源。OER 用于早期材料诊断。</t>
+          <t>Buchwald–Hartwig 与 Doyle CN 是同一实验来源，现有表格候选已停止推进。OER 曾用于早期诊断。</t>
         </is>
       </c>
     </row>
@@ -2293,6 +2391,30 @@
       <c r="B8" s="7" t="inlineStr">
         <is>
           <t>2026-10-09；来源核验日期见各行。本次未对全部网站重新开展实时可达性核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>选题状态</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>这份清单服务多个候选问题，不表示已决定使用哪项数据。题目要求：https://notes.sjtu.edu.cn/f8gmS3wVQ4i4slalHJ-6Yw</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>协议评价</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>BioProt 和 LAB-Bench 提供局部表示或问答任务，不能作为真实实验可实施性与修复成功的完整金标。</t>
         </is>
       </c>
     </row>

--- a/datasets/数据集清单.xlsx
+++ b/datasets/数据集清单.xlsx
@@ -7,14 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实测数据" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推理与交互" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课题索引" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实测数据" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推理与交互" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科学评测补充" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待核线索" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'实测数据'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'推理与交互'!$A$4:$I$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'推理与交互'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'课题索引'!$A$4:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'实测数据'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'实测数据'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'推理与交互'!$A$4:$I$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'推理与交互'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'科学评测补充'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'科学评测补充'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核线索'!$A$4:$I$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'待核线索'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +79,13 @@
       <color rgb="00183153"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -93,10 +109,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -115,9 +132,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -191,6 +213,191 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>来源</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>来源</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A24" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A28" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A29" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+    <comment ref="A34" authorId="0" shapeId="0">
+      <text>
+        <t>Source: 既有数据核验记录，日期与公开来源见本行；2026-10-09按课题补充用途。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets1" displayName="Datasets1" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
@@ -210,8 +417,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Datasets2" displayName="Datasets2" ref="A4:I32" headerRowCount="1">
-  <autoFilter ref="A4:I32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Datasets2" displayName="Datasets2" ref="A4:I34" headerRowCount="1">
+  <autoFilter ref="A4:I34"/>
   <tableColumns count="9">
     <tableColumn id="1" name="名称"/>
     <tableColumn id="2" name="方向"/>
@@ -220,6 +427,42 @@
     <tableColumn id="5" name="过程或标签"/>
     <tableColumn id="6" name="已核验到哪一步"/>
     <tableColumn id="7" name="适合的问题"/>
+    <tableColumn id="8" name="局限性"/>
+    <tableColumn id="9" name="许可、来源与核验日期"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Datasets3" displayName="Datasets3" ref="A4:I13" headerRowCount="1">
+  <autoFilter ref="A4:I13"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="名称"/>
+    <tableColumn id="2" name="方向"/>
+    <tableColumn id="3" name="公开地址"/>
+    <tableColumn id="4" name="数据特征与规模"/>
+    <tableColumn id="5" name="过程或标签"/>
+    <tableColumn id="6" name="已核验到哪一步"/>
+    <tableColumn id="7" name="课题对应与用途"/>
+    <tableColumn id="8" name="局限性"/>
+    <tableColumn id="9" name="许可、来源与核验日期"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Datasets4" displayName="Datasets4" ref="A4:I9" headerRowCount="1">
+  <autoFilter ref="A4:I9"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="名称"/>
+    <tableColumn id="2" name="方向"/>
+    <tableColumn id="3" name="公开地址"/>
+    <tableColumn id="4" name="数据特征与规模"/>
+    <tableColumn id="5" name="过程或标签"/>
+    <tableColumn id="6" name="已核验到哪一步"/>
+    <tableColumn id="7" name="课题对应与用途"/>
     <tableColumn id="8" name="局限性"/>
     <tableColumn id="9" name="许可、来源与核验日期"/>
   </tableColumns>
@@ -514,6 +757,345 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="67" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>按课题查找数据与评测资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>保留原有调研，同时区分补充评测与待核线索；不是已选定方案。3.1/4.1编号来自正文，方向2子项来自原图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>课题要求</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>查哪些资源</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>能检查什么</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>目前还缺什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="95" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>3.1.1 断言与推理单元</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>SciFact、SciRIFF、SciMDR、EntailmentBank（推理与交互）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>抽取断言、前提、中间结论与证据跨度。</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>真实科研推理的完整单元与条件标签仍需补充；解释长不等于每步正确。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="95" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2 科学机理约束</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>WorldTree、ChemCoT、DrugMechDB；XRDBench（科学评测补充）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>规则模板、分子操作、机制关系和材料分析约束。</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>这些资源各有局部规则，没有统一的事实、因果、边界、资源四类金标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="95" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3 三链对齐</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SciFact、QASPER、SciMDR；SCHEMA、SciRigor；实测数据</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>让结论回接原文、数据、测量条件和分析步骤。</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>引用相关与条件一致要分别核验；对象、时间、量值与适用范围不总有标签。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="95" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>方向2·因果方向与结构</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>DrugMechDB、DrugMechCounterfactuals、SciR（推理与交互）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>在明确图和假设下检查方向、路径与干预结果。</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>给定机制图下的正确性不等于真实世界完整因果识别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="95" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>方向2·条件依赖与边界</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>DeReLab（科学评测补充）；SciMDR；化学/材料实测表</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>对照应改变与应保持的结论，检查条件遗漏与过度推广。</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>合成例外和有限查表不能独立证明真实领域规律。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="95" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>方向2·机理一致与反事实</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>DrugMechCounterfactuals、SciR；SCHEMA（科学评测补充）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>在指定规则内改变关系或步骤，观察哪些结论受影响。</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>轨迹编辑、模型重试与现实因果干预需要分别解释。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="95" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>4.1.1 完整性与可操作性</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>BioProt、ScienceWorld；ScienceAgentBench、XRDBench</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>检查步骤、材料、参数、目标与输出，利用局部执行反馈。</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>伪代码相似或计算任务运行成功，不覆盖全部湿实验条件。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="95" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>4.1.2 资源约束与风险边界</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>BioProt、ScienceWorld、Llamole提供局部流程信息；CruxBench仅供查询设计参考</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>定位缺失资源和待补条件，研究何时需要额外信息。</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>当前没有覆盖材料、设备、资质、环境、伦理等全部约束的真实四级风险标签；需另取领域规范和有效案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="95" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>4.1.3 诊断与方案修复</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>LAB-Bench；SCHEMA、DISCERN、ScienceAgentBench、XRDBench</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>输出错点与依据，再核验修复后目标、约束及新增错误。</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>选择正确修复项或诊断正确不等于修复方案可实施；仍需端到端验收。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>课题原文</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>https://notes.sjtu.edu.cn/f8gmS3wVQ4i4slalHJ-6Yw</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>实测数据</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>打开工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>推理与交互</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>打开工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>科学评测补充</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>打开工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>待核线索</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>打开工作表</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>使用说明</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>打开工作表</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I7"/>
@@ -577,7 +1159,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>适合的问题</t>
+          <t>课题对应与用途</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -591,7 +1173,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="106" customHeight="1">
+    <row r="5" ht="125" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Buchwald–Hartwig 工作簿</t>
@@ -624,7 +1206,8 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>条件检索、最优选择、排序反转。</t>
+          <t>3.1.3 条件与证据对齐；仅有限观测表。
+条件检索、最优选择、排序反转。</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -638,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="106" customHeight="1">
+    <row r="6" ht="125" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Doyle 实验室 CN 整理表</t>
@@ -671,7 +1254,8 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>来源核对、条件匿名化、同板比较。</t>
+          <t>3.1.3 来源、条件与样本身份核对。
+来源核对、条件匿名化、同板比较。</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -685,7 +1269,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="106" customHeight="1">
+    <row r="7" ht="125" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>LILA 酸性 OER 薄膜催化剂</t>
@@ -718,7 +1302,8 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>测量口径、结论范围、活性与流失权衡。</t>
+          <t>3.1.3 测量证据与结论范围；机理部分需独立裁定。
+测量口径、结论范围、活性与流失权衡。</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -733,6 +1318,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I7"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -745,13 +1331,14 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -818,7 +1405,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>适合的问题</t>
+          <t>课题对应与用途</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -832,7 +1419,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="106" customHeight="1">
+    <row r="5" ht="125" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>SciMDR 训练集</t>
@@ -865,7 +1452,8 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>证据定位、条件推断、结构化过程监督。</t>
+          <t>3.1.1、3.1.3 科研单元抽取与证据链。
+证据定位、条件推断、结构化过程监督。</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -879,7 +1467,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="106" customHeight="1">
+    <row r="6" ht="125" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>SciMDR-Eval</t>
@@ -912,7 +1500,8 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>科研证据推断的外部评价候选。</t>
+          <t>3.1.3 科研结论与证据对应。
+科研证据推断的外部评价候选。</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -926,7 +1515,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="106" customHeight="1">
+    <row r="7" ht="125" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CrossTrace</t>
@@ -959,7 +1548,8 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>来源约束的科学构思与修订。</t>
+          <t>3.1.1 科研推理单元；重建过程不等于真实发现。
+来源约束的科学构思与修订。</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -973,7 +1563,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="106" customHeight="1">
+    <row r="8" ht="125" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>EntailmentBank</t>
@@ -1006,7 +1596,8 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>前提检索、推理图、依赖边诊断。</t>
+          <t>3.1.1、3.1.2 前提—中间结论结构。
+前提检索、推理图、依赖边诊断。</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1020,7 +1611,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="106" customHeight="1">
+    <row r="9" ht="125" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>WorldTree / ExplanationBank</t>
@@ -1053,7 +1644,8 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>检索库与多前提组合基线。</t>
+          <t>3.1.2、3.1.3 事实模板与组合依据。
+检索库与多前提组合基线。</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1067,7 +1659,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="106" customHeight="1">
+    <row r="10" ht="125" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>QASC</t>
@@ -1100,7 +1692,8 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>短证据组合基线。</t>
+          <t>3.1.3 短证据组合。
+短证据组合基线。</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1114,7 +1707,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="106" customHeight="1">
+    <row r="11" ht="125" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>eQASC</t>
@@ -1147,7 +1740,8 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>推理链验证器候选。</t>
+          <t>3.1.3 证据链有效性。
+推理链验证器候选。</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1161,7 +1755,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="106" customHeight="1">
+    <row r="12" ht="125" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>ScienceWorld</t>
@@ -1194,7 +1788,8 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>操作前提、实验规划、反馈更新。</t>
+          <t>4.1.1、4.1.3 模拟操作与修复验收。
+操作前提、实验规划、反馈更新。</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1208,7 +1803,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="106" customHeight="1">
+    <row r="13" ht="125" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>DiscoveryWorld</t>
@@ -1241,7 +1836,8 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>主动实验与信息发现。</t>
+          <t>4.1.1、4.1.3 模拟实验过程。
+主动实验与信息发现。</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1255,7 +1851,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="106" customHeight="1">
+    <row r="14" ht="125" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>SciR</t>
@@ -1288,7 +1884,8 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>结构化科学推理诊断。</t>
+          <t>方向2：形式前提下的演绎、归纳和因果诊断。
+结构化科学推理诊断。</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1302,7 +1899,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="106" customHeight="1">
+    <row r="15" ht="125" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Llamole-MolQA</t>
@@ -1335,7 +1932,8 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>受限反应路线组合、结构约束。</t>
+          <t>3.1.2、4.1.1 分子约束与路线结构。
+受限反应路线组合、结构约束。</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1349,7 +1947,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="106" customHeight="1">
+    <row r="16" ht="125" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>ChemCoTDataset</t>
@@ -1382,7 +1980,8 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>专用化学操作链训练候选。</t>
+          <t>3.1.2 分子操作约束。
+专用化学操作链训练候选。</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1396,7 +1995,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="106" customHeight="1">
+    <row r="17" ht="125" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>ChemCoTBench</t>
@@ -1429,7 +2028,8 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>化学操作迁移评价候选。</t>
+          <t>3.1.2 分子操作和性质约束评价。
+化学操作迁移评价候选。</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1443,7 +2043,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="106" customHeight="1">
+    <row r="18" ht="125" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ether0-benchmark</t>
@@ -1476,7 +2076,8 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>现成化学评测与奖励工具。</t>
+          <t>3.1.2 工具可检查的分子约束。
+现成化学评测与奖励工具。</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1490,7 +2091,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="106" customHeight="1">
+    <row r="19" ht="125" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>MatSciChartQ-Traces</t>
@@ -1523,7 +2124,8 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>图表读取与数值比较。</t>
+          <t>3.1.3 图表证据与数值结论。
+图表读取与数值比较。</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1537,7 +2139,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="106" customHeight="1">
+    <row r="20" ht="125" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>MatSciBench</t>
@@ -1570,7 +2172,8 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>材料侧评测备选。</t>
+          <t>3.1.1、3.1.2 材料问答的求解步骤。
+材料侧评测备选。</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1584,7 +2187,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="106" customHeight="1">
+    <row r="21" ht="125" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>ChemAgent / SciBench 示例</t>
@@ -1617,7 +2220,8 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>数值计算和单位检查原型。</t>
+          <t>3.1.2 教材计算与单位约束的局部检查。
+数值计算和单位检查原型。</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1631,7 +2235,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="106" customHeight="1">
+    <row r="22" ht="125" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>BioReason KEGG</t>
@@ -1664,7 +2268,8 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>序列到通路的证据推断。</t>
+          <t>3.1.1、方向2：生物解释与通路对应；非逐步机理金标。
+序列到通路的证据推断。</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1678,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="106" customHeight="1">
+    <row r="23" ht="125" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>BioReason-Pro 训练集</t>
@@ -1711,7 +2316,8 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>蛋白功能解释训练候选。</t>
+          <t>3.1.1、3.1.3 蛋白功能解释与多源证据。
+蛋白功能解释训练候选。</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1725,7 +2331,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="106" customHeight="1">
+    <row r="24" ht="125" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
           <t>BioReason-Pro 测试集</t>
@@ -1758,7 +2364,8 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>独立蛋白任务评价候选。</t>
+          <t>3.1.3 功能结论与证据的外部评价候选。
+独立蛋白任务评价候选。</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1772,7 +2379,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="106" customHeight="1">
+    <row r="25" ht="125" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>DrugMechCounterfactuals</t>
@@ -1805,7 +2412,8 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>机制边干预、依赖传播。</t>
+          <t>方向2：指定机制图下的反事实关系推断。
+机制边干预、依赖传播。</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1819,7 +2427,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="106" customHeight="1">
+    <row r="26" ht="125" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>DrugMechDB</t>
@@ -1852,7 +2460,8 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>机制结构与来源支持核对。</t>
+          <t>方向2：机制方向、关系与路径表示。
+机制结构与来源支持核对。</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1866,7 +2475,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="106" customHeight="1">
+    <row r="27" ht="125" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>SciInstruct</t>
@@ -1899,7 +2508,8 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>补充科学解题监督。</t>
+          <t>3.1.1 科学题求解过程辅助语料。
+补充科学解题监督。</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1913,7 +2523,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="106" customHeight="1">
+    <row r="28" ht="125" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
           <t>SciReasoner cold-start</t>
@@ -1946,7 +2556,8 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>合成过程质量审计。</t>
+          <t>3.1.1 合成过程辅助语料。
+合成过程质量审计。</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1960,7 +2571,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="106" customHeight="1">
+    <row r="29" ht="125" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>ScienceQA</t>
@@ -1993,7 +2604,8 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>多模态解释与基础能力检查。</t>
+          <t>3.1.1 基础科学解释单元。
+多模态解释与基础能力检查。</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2007,7 +2619,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="106" customHeight="1">
+    <row r="30" ht="125" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
           <t>SciRIFF</t>
@@ -2040,7 +2652,8 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>文献任务训练与格式基线。</t>
+          <t>3.1.1 科研文本抽取与结构化任务。
+文献任务训练与格式基线。</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2054,7 +2667,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="106" customHeight="1">
+    <row r="31" ht="125" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>SciFact</t>
@@ -2087,7 +2700,8 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>证据检索、主张核验基线。</t>
+          <t>3.1.1、3.1.3 断言与证据支持关系。
+证据检索、主张核验基线。</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2101,7 +2715,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="106" customHeight="1">
+    <row r="32" ht="125" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>QASPER</t>
@@ -2134,7 +2748,8 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>长文证据定位与问答。</t>
+          <t>3.1.3 长文问答与支持段落。
+长文证据定位与问答。</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2148,7 +2763,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="120" customHeight="1">
+    <row r="33" ht="125" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>BioProt / BioPlanner</t>
@@ -2181,7 +2796,8 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>候选 03：步骤顺序、参数完整性、协议重建的基础对照。</t>
+          <t>4.1.1 实验协议步骤和参数结构。
+候选 03：步骤顺序、参数完整性、协议重建的基础对照。</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2195,7 +2811,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="120" customHeight="1">
+    <row r="34" ht="125" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>LAB-Bench（含 ProtocolQA）</t>
@@ -2228,7 +2844,8 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>候选 03：协议错误诊断与修复选择；文献、表格等子任务可作局部评价。</t>
+          <t>4.1.1、4.1.3 协议错误诊断与修复选择。
+候选 03：协议错误诊断与修复选择；文献、表格等子任务可作局部评价。</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2283,19 +2900,20 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId31"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2418,7 +3036,921 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>清单构成</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>原有资源全部保留；科学评测补充收录既有文献中的任务入口；待核线索保留旧筛选中的暂缓项目与原因，不视为已可训练数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>入口类型</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>公开地址可能指向数据仓库、项目或论文。以“已核验到哪一步”列为准；论文报告规模和实际取得样本分开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>课题索引</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>从首张工作表按课题查找。通用检索、模拟环境、科学实测和机制图各自提供局部证据，不合并成一个科学正确性指标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>覆盖缺口</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>资源、环境、资质与风险边界的真实标签仍不足；尚无一个清单条目完整覆盖可直接执行、需补充条件、需专家复核、不可实施四类。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>科学评测补充</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>按既有来源恢复；入口可能是数据仓库、工具或论文。先看核验状态，再决定是否适用于训练或评价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>公开地址</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>数据特征与规模</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>过程或标签</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>已核验到哪一步</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>课题对应与用途</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>局限性</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>许可、来源与核验日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="125" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ScienceAgentBench</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>计算实验</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>https://osu-nlp-group.github.io/ScienceAgentBench/</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>论文报告从 44 篇论文构造 102 个 Python 科学任务，覆盖四个学科。</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>任务说明、科学数据、参考程序与任务验收；不是湿实验执行标签。</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录核对任务构造与评价；入口来自论文，未逐项下载重跑。</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>4.1.1、4.1.3：分开检查代码执行、科学任务完成和修复后的结果。</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>公开依赖和任务标准限制覆盖；可运行不等于科学语义正确，重试择优需单列。</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R36；arXiv:2410.05080v3；各底层数据许可需逐项核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DiscoveryBench</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>科学发现</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/allenai/discoverybench</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>论文报告 264 个真实任务、903 个合成任务，提供数据、元信息与发现目标。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>参考假设及条件、变量、关系等评价维度；部分评价使用模型裁判。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录核对任务与官方发布地址；未逐行审计。</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3、方向2适用边界：核对假设条件与数据证据是否一致。</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>匹配参考假设不穷尽正确发现；模型评分不等于科学真值，也不是现实发现成功率。</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R37；arXiv:2407.01725v1；论文说明数据 ODC-BY、代码 Apache-2.0。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="125" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SCHEMA</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>科学代理轨迹</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/circles-post/SCHEMA</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>科学任务的执行轨迹、断言与依赖图；本次不将单模型评测题数写成全部数据规模。</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>断言核验、拓扑评价与局部编辑后的恢复结果。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录；仓库入口见原文，数据包与全部标签尚未逐项核验。</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>3.1.1、3.1.3、4.1.3：结构化轨迹、证据支持与错误传播诊断。</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>编辑同时可能增加信息和重试；恢复不证明唯一根因，图结构也不是完整科学因果。</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R30；arXiv:2608.00711v1；具体数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="125" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>DeReLab</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>条件更新与规则推理</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/Jayanta47/DeReLab</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>参数化规则图生成多轮任务；应按生成器和配置记录规模。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>结论真值与新增信息加强、削弱或无关的作用标签。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录与论文中的仓库入口；未重新生成全量任务。</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>方向2条件依赖：同时检验应更新和应保持的结论。</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>规则合成语境不等于真实科学机理；问法和询问顺序影响表现。</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R47；arXiv:2608.30413v1；代码和派生数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="125" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>DISCERN</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>科学数据与分析诊断</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.33357v1</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>论文报告 79 个数据预处理任务、102 个分析核验任务和 22 个假设档案。</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>干净对照、受控数据缺陷、分析混杂与对抗审阅；三层分别评价。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>已核全文设计；当前填写论文入口，完整数据包的取得与许可仍待核实。</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2、4.1.3：定位数据、分析和假设层面的错误并分别验收。</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>三个层次不是一条已验证的端到端修复链；发现错误不能直接记为修复完成。</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R12；论文入口不是原始数据下载地址，数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="125" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SciRigor</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>科研证据链</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.06192v1</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>以论文图表问题为单位组织数据、分析、结果和断言；数据条数尚未独立核验。</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>分析依赖、结果槽位、图表要求与原子断言，用于分环节检查。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>已核全文方法；当前为论文入口，完整发布包和样本未逐条核验。</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3、4.1.3：核查数据—变换—结果—结论，并验证修复后的支持关系。</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>依赖公开较完整案例；复跑原代码也不自动保证原研究的科学结论成立。</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R82；具体资源地址与数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="125" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>HalluPeer</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>科学评审错误</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/Lin-TzuLing/HalluPeer</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>科学论文与评审的分类注错、检测任务，另有真实评审评价。</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>错误类型与局部检测标签；合成和自然样本必须分开使用。</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录与原文仓库入口；未下载审计全部样本。</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>3.1.1、4.1.3：借鉴断言核验、错误标签与正确样本误报评价。</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>语义改动未必使断言为假；学科覆盖有限，评审错误标签不是实验风险分级。</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R35；arXiv:2609.03580v1；具体数据及上游论文条款待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="125" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CruxBench</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>信息获取</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/ai-prophet/cruxbench</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>论文报告 293 个目标预测问题，评价提出关键子问题的信息价值。</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>子问题、可解析答案、信息价值与目标判断的变化。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>依据既有全文记录与原文仓库入口；未逐项核验全部数据文件。</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3、4.1.2：把缺失条件转成待获取信息，并评价查询成本与最终判断。</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>预测问题的信息价值不等于科学因果识别；缺少真实实验资源、资质和风险等级金标。</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R112；arXiv:2609.35879v1；具体数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="125" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>XRDBench / AutoXRD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>材料表征工作流</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/Stephen-SMJ/XRDBench</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>原文报告 100 个 XRD 问答与 34 个可执行工作流；问答包含程序构造与实验资料。</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>XRD 数据、结构、精修任务与分阶段验收契约。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>既有记录取得官方 README 和 QA/工作流契约；未运行完整精修评价。</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2、4.1.1、4.1.3：数值拟合之外检查物理约束、操作与修复结果。</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>复合分数不是错误发生率；精修状态不等于真实样品状态，执行依赖与领域条件需固定。</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 文献记录 R88；arXiv:2609.00070；各数据与执行工具许可分别核验。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="49" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>待核线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>按既有来源恢复；入口可能是数据仓库、工具或论文。先看核验状态，再决定是否适用于训练或评价。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>公开地址</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>数据特征与规模</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>过程或标签</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>已核验到哪一步</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>课题对应与用途</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>局限性</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>许可、来源与核验日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="125" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ChemDFM-R / ChemFG-Tool</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>化学工具与过程语料线索</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2507.21990v4</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>论文描述混合来源蒸馏与官能团工具；模型、工具和训练过程语料是不同资产。</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>答案条件下的合成推理；尚无本次已取得的蒸馏训练记录。</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>旧化学报告已核数据公开声明：明确给出工具；未核实蒸馏过程训练集下载。</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2：官能团检查的工具候选；现阶段不作为已取得的过程训练集。</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>模型开源或训练量在论文中出现，不能证明相应训练文件已公开。</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30 化学与材料数据核验报告；恢复的是调研结论，当前为论文入口；数据许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>RetroDFM-R 过程语料与推理集</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>逆合成</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2507.17448v2</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>论文报告 122,812 条冷启动示范；公开来源、推理集与冷启动 CoT 需区分。</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>教师看到真实反应物后生成的解释；冷启动训练文件未在旧核验中取得。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>旧报告核到原始来源及 OpenDFM/retrodfm-R-inference 线索，未确认冷启动文件下载。</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2、4.1.1：路线结构与操作约束的备选；不能直接列为可训练过程数据。</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>训练路径示例不等于文件已发布；逆合成路线也不等于完整实验操作方案。</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30 化学与材料数据核验报告；当前为论文入口，实际数据地址和条款待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="125" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>SciRAG-SSLI / DeepEra</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>科研检索与证据相关性</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.16478v1</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>论文报告约 300K 科学问答、10 个学科，由科学语料与干扰上下文构造。</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>自然检索上下文及模型生成的语义相似、逻辑无关干扰。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>旧报告已读全文；未核实可下载数据包和逐步过程文件。</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3：检验主题相关但逻辑无关的证据是否误入支持链。</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>模型生成干扰与自然科学错误不同；论文规模不等于已取得数据量。</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30 科学推理数据筛选报告；当前为论文入口，数据发布与许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="125" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sci-MMR</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>多模态科研证据</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2609.11243v2</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>旧检索摘要报告 235 个多跳任务、四个科学学科；论证图连接断言、引文和图像区域。</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>摘要描述结构化证据图；实际字段、切分与标签尚未核验。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>仅恢复旧检索题录和摘要线索；未取得数据样本。</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>3.1.3：跨文字与图表核验完整证据组合，作为待核候选。</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>摘要指标不能替代数据审计；未确认完整条件链标签或训练适用性。</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30 检索记录；arXiv:2609.11243v2；数据地址及许可待核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="125" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>SCIPRM70K / SCI-PRM</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>科学工具过程监督</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2606.04579v2</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>旧检索摘要提出 SCIPRM70K 科学工具轨迹；未独立计数文件。</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>推理与工具执行交织，论文称覆盖工具选择、执行和结果解释的过程标签。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>仅恢复旧检索题录和摘要线索；未取得训练记录、标注说明或验证器。</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>3.1.2、4.1.3：过程检查与奖励的待核候选；不能先当作科学正确性金标。</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>过程奖励是否可靠、数据是否可得和是否泄露答案均需核验。</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30 检索记录；arXiv:2606.04579v2；数据地址及许可待核。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/datasets/数据集清单.xlsx
+++ b/datasets/数据集清单.xlsx
@@ -7,23 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课题索引" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实测数据" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推理与交互" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科学评测补充" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待核线索" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐项下载" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课题索引" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实测数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推理与交互" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科学评测补充" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待核线索" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'课题索引'!$A$4:$D$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'实测数据'!$A$4:$I$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'实测数据'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'推理与交互'!$A$4:$I$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'推理与交互'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'科学评测补充'!$A$4:$I$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'科学评测补充'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'待核线索'!$A$4:$I$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'待核线索'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'课题索引'!$A$4:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'实测数据'!$A$4:$I$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'实测数据'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'推理与交互'!$A$4:$I$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'推理与交互'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'科学评测补充'!$A$4:$I$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'科学评测补充'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'待核线索'!$A$4:$I$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'待核线索'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,8 +87,24 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00202B38"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00174E7A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +114,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00183153"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00245A81"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +163,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -399,7 +438,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets1" displayName="Datasets1" ref="A4:I7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DatasetDownloads" displayName="DatasetDownloads" ref="A4:G51" headerRowCount="1">
+  <autoFilter ref="A4:G51"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="名称"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="独立说明"/>
+    <tableColumn id="4" name="主要下载地址"/>
+    <tableColumn id="5" name="取得状态"/>
+    <tableColumn id="6" name="访问方法与范围"/>
+    <tableColumn id="7" name="核对日期"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Datasets1" displayName="Datasets1" ref="A4:I7" headerRowCount="1">
   <autoFilter ref="A4:I7"/>
   <tableColumns count="9">
     <tableColumn id="1" name="名称"/>
@@ -416,8 +471,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Datasets2" displayName="Datasets2" ref="A4:I34" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Datasets2" displayName="Datasets2" ref="A4:I34" headerRowCount="1">
   <autoFilter ref="A4:I34"/>
   <tableColumns count="9">
     <tableColumn id="1" name="名称"/>
@@ -434,8 +489,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Datasets3" displayName="Datasets3" ref="A4:I13" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Datasets3" displayName="Datasets3" ref="A4:I13" headerRowCount="1">
   <autoFilter ref="A4:I13"/>
   <tableColumns count="9">
     <tableColumn id="1" name="名称"/>
@@ -452,8 +507,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Datasets4" displayName="Datasets4" ref="A4:I9" headerRowCount="1">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Datasets4" displayName="Datasets4" ref="A4:I9" headerRowCount="1">
   <autoFilter ref="A4:I9"/>
   <tableColumns count="9">
     <tableColumn id="1" name="名称"/>
@@ -759,6 +814,1939 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="86" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>逐项数据下载索引</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>47 项均有独立说明；未取得的数据不以论文或代码代替。路径核对：2026-10-09。</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="11" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="11" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>独立说明</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>主要下载地址</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>取得状态</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>访问方法与范围</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>核对日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="82" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Buchwald–Hartwig 工作簿</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>实测化学与材料</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>01-实测化学与材料/01-Buchwald-Hartwig.md</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/rxn4chemistry/rxn_yields/HEAD/data/Buchwald-Hartwig/Dreher_and_Doyle_input_data.xlsx</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>可直接下载；目录或压缩包包含其余文件。</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="82" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Doyle 实验室 CN 整理表</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>实测化学与材料</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>01-实测化学与材料/02-Doyle-CN.md</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/doyle-lab-ucla/ochem-data/HEAD/CN/raw.csv</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>可直接下载；目录或压缩包包含其余文件。</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="82" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>LILA 酸性 OER 薄膜催化剂</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>实测化学与材料</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>01-实测化学与材料/03-LILA-OER.md</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/fl97inc/lila_oer_manuscript/tree/HEAD/data</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>前三个文件分别用于筛选记录、长时曲线和 XRD；其余数据见完整目录。</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="82" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>SciMDR 训练集</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/04-SciMDR-训练集.md</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/scimdr/SciMDR/tree/main</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>图像与原文另在 arxiv/、nature/ 的压缩包中；完整下载命令会一并取得，体积较大。</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="82" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>SciMDR-Eval</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/05-SciMDR-Eval.md</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/scimdr/SciMDR-Eval/tree/main</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>图像在 images/；只下载 JSONL 不包含配套图像。完整下载命令会一并取得。</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="82" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>CrossTrace</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/06-CrossTrace.md</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/andrewbouras/crosstrace/tree/HEAD/data</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>all_traces 保留来源信息；另外三个文件提供原始训练、验证和测试划分。balanced 版本含重复，单独比较。</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="82" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>EntailmentBank</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/07-EntailmentBank.md</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/allenai/entailment_bank/tree/HEAD/data/public_dataset/entailment_trees_emnlp2021_data_v2</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>已列 task_1 三个划分和事实库；task_2、task_3 在完整目录中，是同一题目的不同输入设置。</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="82" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>WorldTree / ExplanationBank</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/08-WorldTree.md</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>https://cognitiveai.org/dist/WorldtreeExplanationCorpusV2.1_Feb2020.zip</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>官方外部下载</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>官方页面提供的 V2.1 压缩包；与 Mercury 题目配套使用时须遵守额外 EULA。</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="82" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>QASC</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/09-QASC.md</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/allenai/qasc/tree/main</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>题目优先用 AI2 官方 HF 文件。17M 句检索语料需另取：原仓库公布的旧地址 http://data.allenai.org/downloads/qasc/qasc_corpus.tar.gz 本次未能连通，HF 下载命令不包含该语料。test 不含答案和事实标注，正式测试遵循官方评测流程。</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="82" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>eQASC</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/10-eQASC.md</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/1Mal9Xi4VA8LRCsmQSisF3D0_I_ir_WJm?usp=sharing</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>官方外部下载</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>进入官方指定网盘，选中数据文件下载；完整包未在本次下载。</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="82" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ScienceWorld</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/11-ScienceWorld.md</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/allenai/ScienceWorld/HEAD/goldpaths/goldpaths-all.zip</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>轨迹与环境分开下载；重放时固定 ScienceWorld 版本。</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="82" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>DiscoveryWorld</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/12-DiscoveryWorld.md</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/drive/folders/14FucVzVCm1HZ0EfPEKoPwdRsFnZi769k?usp=drive_link</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>官方外部下载</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>按 agent 和难度下载分包；人类记录在 human-performance/、human-raw/。此地址提供数据，单独的视频包不能替代轨迹。完整包未在本次下载。</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="82" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>SciR</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/13-SciR.md</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/sci-reason/scir/tree/main</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>下列是因果、演绎主任务文件示例；归纳和难度变体见完整目录。数据卡限制为评测用途，不作为训练集。</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="82" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Llamole-MolQA</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/14-Llamole-MolQA.md</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/liuganghuggingface/Llamole-MolQA/tree/main</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="82" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>ChemCoTDataset</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/15-ChemCoTDataset.md</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/IDEA-AI4S/ChemCoTDataset/tree/main</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>需申请权限</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>先在官方数据页登录并申请访问，通过后运行下方命令。文件名已由公开目录核对；未登录请求返回 401，未取得原始记录。下列仅是文件示例，完整任务见目录。</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="82" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>ChemCoTBench</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/16-ChemCoTBench.md</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/IDEA-AI4S/ChemCoTBench/tree/main</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>需申请权限</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>先在官方数据页登录并申请访问，通过后运行下方命令。文件名已由公开目录核对；未登录请求返回 401，未取得原始记录。下列仅是文件示例，完整任务见目录。</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="82" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>ether0-benchmark</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/17-ether0-benchmark.md</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/futurehouse/ether0-benchmark/tree/main</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="82" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>MatSciChartQ-Traces</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/18-MatSciChartQ-Traces.md</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/translorentz/matsci-visual-reasoning-nc/tree/main</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>下列是清单和一个图表分区；完整目录包含 12 个图表类型文件。</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="82" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>MatSciBench</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/19-MatSciBench.md</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/JunkaiZ/MatSciBench/tree/main</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="82" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>ChemAgent / SciBench 示例</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/20-ChemAgent-SciBench示例.md</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/gersteinlab/ChemAgent/tree/HEAD/dataset</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>单文件是此前核验的 16 条 Atkins 示例；目录还含其他 SciBench 题目及示例，不把它们合计为已核验过程数据。</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="82" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>BioReason KEGG</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>生物机制</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>05-生物机制/21-BioReason-KEGG.md</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/wanglab/kegg/tree/main</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="82" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>BioReason-Pro 训练集</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>生物机制</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>05-生物机制/22-BioReason-Pro-训练集.md</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/wanglab/bioreason-pro-sft-reasoning-data/tree/main</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="82" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>BioReason-Pro 测试集</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>生物机制</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>05-生物机制/23-BioReason-Pro-测试集.md</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/wanglab/bioreason-pro-test-data/tree/main</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>可按文件下载；下方命令可下载完整数据仓库。</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="82" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>DrugMechCounterfactuals</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>生物机制</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>05-生物机制/24-DrugMechCounterfactuals.md</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/czi-ai/DrugMechCounterfactuals/tree/HEAD/Data/Counterfactuals</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>下列 JSON 是已读样本文件；全量 AddLink、change、delete 和 factuals 在同一目录。部分实验还需要上游 DrugMechDB。</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="82" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>DrugMechDB</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>生物机制</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>05-生物机制/25-DrugMechDB.md</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/SuLab/DrugMechDB/HEAD/indication_paths.yaml</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>可直接下载；目录或压缩包包含其余文件。</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="82" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>SciInstruct</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/26-SciInstruct.md</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/zd21/SciInstruct/tree/main</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>三类数据分别下载。课题优先核查物理化学部分，不能把数学和证明数据都计为科学机理监督。</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="82" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>SciReasoner cold-start</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/27-SciReasoner-cold-start.md</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/SciReason/SciLM-CoT_ColdStart/tree/main</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>下列是此前抽样的 BBBP 和蛋白溶解性文件，其余任务见完整目录。</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="82" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>ScienceQA</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/28-ScienceQA.md</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/lupantech/ScienceQA/HEAD/data/scienceqa/problems.json</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>题目文本、划分和图像需配套使用；只下载 problems.json 不包含图像。</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="82" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>SciRIFF</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/29-SciRIFF.md</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/allenai/SciRIFF/tree/main</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>下列为 4096 上下文版本；8192、16384 版本见完整目录，不应当作额外独立数据。</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="82" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>SciFact</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/30-SciFact.md</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>https://scifact.s3-us-west-2.amazonaws.com/release/latest/data.tar.gz</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>数据包含 corpus.jsonl 与 claims_train/dev/test.jsonl；test 无公开标签。</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="82" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>QASPER</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/31-QASPER.md</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>https://qasper-dataset.s3.us-west-2.amazonaws.com/qasper-train-dev-v0.3.tgz</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>实际压缩包地址来自 AI2 官方 Hugging Face 加载脚本；不是该仓库里的 dummy 小样本。</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="82" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>BioProt / BioPlanner</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/32-BioProt-BioPlanner.md</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/bioplanner/bioplanner/tree/HEAD/bioprot</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>目录已核到 100 个协议 JSON；ZIP 解压后取 bioprot/，其余为代码与实验文件。</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="82" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>LAB-Bench（含 ProtocolQA）</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/33-LAB-Bench.md</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/futurehouse/lab-bench/tree/main</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>逐项列出八个子集文件。发布路径名为 train，但这些是基准评测题，不能据此当作训练材料。</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="82" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>ScienceAgentBench</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/34-ScienceAgentBench.md</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/osunlp/ScienceAgentBench/tree/main</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>输入公开；完整包受限</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>优先使用官方 2026-04-30 更新的 verified 划分，并配套 benchmark_verified.zip。HF 只提供输入注释；完整数据、参考程序和评测材料在下方外部包，解压密码为官方公开的 scienceagentbench。外部包本次请求返回 401，需在浏览器确认访问权限。</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="82" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>DiscoveryBench</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/35-DiscoveryBench.md</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/allenai/discoverybench/tree/main</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>参考答案与一个真实数据表如上。完整数据及元信息在 discoverybench/；真实/合成、开发/测试分别保留，实际运行需下载完整仓库。</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="82" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>SCHEMA</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/36-SCHEMA.md</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/circles-post/SCHEMA/archive/HEAD.zip</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>仅核到代码</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>完整 SCHEMA 数据包：尚未找到可核实的公开下载路径。官方仓库提供构建与评价代码；下载脚本取得的是上游基准，不能当作 SCHEMA 完整轨迹与标注。</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="82" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>DeReLab</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/37-DeReLab.md</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/Jayanta47/DeReLab/tree/HEAD/datasets</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>下列为规则推理和线性继承样例；树继承、反序、实体替换和多种随机种子版本见完整目录。</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="82" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>DISCERN</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/38-DISCERN.md</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/discern-bench-anon/discern-benchmark/tree/main</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>下列为任务总表和单轨清单，不能替代完整输入。任务输入与结果在 tracks/；完整运行前按 EXTERNAL_RUNTIME.md 另取 CADD、ESM 等依赖。下载命令只取发布仓库，不会代为运行付费模型。</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="82" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>SciRigor</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/39-SciRigor.md</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>暂无已核实数据下载地址</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>未找到数据包</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>下载路径：暂无已核实地址。已核论文全文及公开仓库检索，尚未找到能确认属于这篇 SciRigor 论文的数据下载包。检索到的同名 SciRigorBench 属于不同内容，未混用。</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="82" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>HalluPeer</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/40-HalluPeer.md</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>暂无已核实数据下载地址</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>未找到数据包</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>下载路径：暂无已核实地址。官方仓库当前仅有 README 与 .gitignore，没有数据文件或下载说明。需等待作者补充发布，不能把仓库 ZIP 当作数据包。</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="82" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>CruxBench</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>实验流程与科学代理</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>06-实验流程与科学代理/41-CruxBench.md</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/ai-prophet/cruxbench/tree/HEAD/data</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>题目与新闻上下文可单独下载；完整 ZIP 另含价格序列、子问题输出及评价脚本。</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="82" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>XRDBench / AutoXRD</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/42-XRDBench.md</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>https://github.com/Stephen-SMJ/XRDBench/tree/HEAD/files</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>问答、工作流契约和 files/ 中的实验附件必须配套。ZIP 包含这些输入及展示代码，完整精修运行仍需按官方要求安装工具。</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="82" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>ChemDFM-R / ChemFG-Tool</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/43-ChemDFM-R-ChemFG-Tool.md</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/OpenDFM/ChemFG-Tool/HEAD/functional_group_list.tsv</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>仅核到工具</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>可下载官能团规则表和识别工具。ChemDFM-R 蒸馏训练过程数据：尚未找到已核实的下载路径；不能将工具表当作训练 CoT。</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="82" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>RetroDFM-R 过程语料与推理集</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>化学与材料推理</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>04-化学与材料推理/44-RetroDFM-R.md</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/OpenDFM/retrodfm-R-inference/tree/main</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>评测文件公开</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>官方确认这些是推理/评测文件。冷启动 122,812 条 CoT 训练语料仍未核实公开下载；aug1、aug20 是增强设置，不能算独立数据源。</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="82" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SciRAG-SSLI / DeepEra</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/45-SciRAG-SSLI-DeepEra.md</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>暂无已核实数据下载地址</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>未找到数据包</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>下载路径：暂无已核实地址。已核论文全文、Hugging Face 与 GitHub 精确名称检索，尚未找到 SciRAG-SSLI 的官方数据包。论文中的约 300K 是作者报告规模。</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="82" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Sci-MMR</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>科研文献与证据</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>02-科研文献与证据/46-Sci-MMR.md</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>暂无已核实数据下载地址</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>未找到数据包</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>下载路径：暂无已核实地址。已核论文全文及 Hugging Face、GitHub 名称检索，尚未找到能确认来源的数据下载包。保留为候选线索。</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="82" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>SCIPRM70K / SCI-PRM</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>基础科学与规则推理</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>03-基础科学与规则推理/47-SCIPRM70K.md</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/InternScience/SCIPRM70K/tree/main</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>公开文件</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>已找到与论文官方 GitHub 同属 InternScience 的数据仓库；原始文件未全量统计。仓库 README 报告 17,818 条轨迹、86,314 个标注步骤，名称中的 70K 不能直接当作轨迹数。</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId90"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId91"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1092,7 +3080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1338,7 +3326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2375,7 +4363,7 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30；使用前单独核测试数据卡许可。</t>
+          <t>数据卡 Apache-2.0（2026-10-09）；底层蛋白与数据库来源条款另核。</t>
         </is>
       </c>
     </row>
@@ -2907,7 +4895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3056,7 +5044,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>公开地址可能指向数据仓库、项目或论文。以“已核验到哪一步”列为准；论文报告规模和实际取得样本分开。</t>
+          <t>“逐项下载”是当前下载索引，列明文件、申请入口、仅代码/工具及暂无数据包。原资料表保留来源与样本核验记录；历史待核条目的新发现见下载索引。</t>
         </is>
       </c>
     </row>
@@ -3068,7 +5056,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>从首张工作表按课题查找。通用检索、模拟环境、科学实测和机制图各自提供局部证据，不合并成一个科学正确性指标。</t>
+          <t>“逐项下载”提供47项独立说明与下载地址；“课题索引”继续按课题查资源与缺口。各类资源提供局部证据，不能合成一个科学正确性指标。</t>
         </is>
       </c>
     </row>
@@ -3089,7 +5077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3183,7 +5171,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://osu-nlp-group.github.io/ScienceAgentBench/</t>
+          <t>https://huggingface.co/datasets/osunlp/ScienceAgentBench</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3198,7 +5186,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>依据既有全文记录核对任务构造与评价；入口来自论文，未逐项下载重跑。</t>
+          <t>既有全文记录已核任务与评价；本次核到 verified Parquet 和完整材料的官方外部下载入口，未重跑任务。</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -3292,7 +5280,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>依据既有全文记录；仓库入口见原文，数据包与全部标签尚未逐项核验。</t>
+          <t>既有全文记录已核设计；2026-10-09 官方仓库树主要为构建/评价代码，未核到完整任务、轨迹与标注发布包。</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -3371,7 +5359,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2609.33357v1</t>
+          <t>https://huggingface.co/datasets/discern-bench-anon/discern-benchmark</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3386,7 +5374,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>已核全文设计；当前填写论文入口，完整数据包的取得与许可仍待核实。</t>
+          <t>既有全文记录已核设计；2026-10-09 核到匿名官方发布仓库、任务总表和分轨文件目录，未全量审计输入或重跑评价。</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -3401,7 +5389,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 文献记录 R12；论文入口不是原始数据下载地址，数据许可待核。</t>
+          <t>DISCERN 自有代码和文档 MIT；底层数据逐项见官方 DATA_SOURCES_AND_LICENSES.md 与 THIRD_PARTY_NOTICES.md；2026-10-09。</t>
         </is>
       </c>
     </row>
@@ -3423,7 +5411,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>以论文图表问题为单位组织数据、分析、结果和断言；数据条数尚未独立核验。</t>
+          <t>论文报告 100 个案例、六个领域、17 个子领域；每例组织数据、分析、结果、图表与断言。数据行数未独立统计。</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3433,7 +5421,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>已核全文方法；当前为论文入口，完整发布包和样本未逐条核验。</t>
+          <t>既有全文记录已核方法；本次仍未找到能确认归属的完整数据包。</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -3480,7 +5468,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>依据既有全文记录与原文仓库入口；未下载审计全部样本。</t>
+          <t>既有全文记录已核任务设计；2026-10-09 官方仓库仅含说明与忽略文件，未核到可下载数据。</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -3618,7 +5606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3712,7 +5700,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2507.21990v4</t>
+          <t>https://github.com/OpenDFM/ChemFG-Tool</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3727,7 +5715,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>旧化学报告已核数据公开声明：明确给出工具；未核实蒸馏过程训练集下载。</t>
+          <t>已核论文公开声明；2026-10-09 核到 ChemFG-Tool 规则表及代码，未核实蒸馏训练 CoT 文件。</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -3742,7 +5730,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 化学与材料数据核验报告；恢复的是调研结论，当前为论文入口；数据许可待核。</t>
+          <t>工具许可见 ChemFG-Tool 仓库 LICENSE；蒸馏训练集的取得与使用条款仍未核实；2026-10-09。</t>
         </is>
       </c>
     </row>
@@ -3759,7 +5747,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2507.17448v2</t>
+          <t>https://huggingface.co/datasets/OpenDFM/retrodfm-R-inference</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3774,7 +5762,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>旧报告核到原始来源及 OpenDFM/retrodfm-R-inference 线索，未确认冷启动文件下载。</t>
+          <t>2026-10-09 核到官方推理集三个 JSONL 路径及仓库说明；尚未核到冷启动 CoT 训练文件，也未全量审计推理集。</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -3789,7 +5777,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 化学与材料数据核验报告；当前为论文入口，实际数据地址和条款待核。</t>
+          <t>官方推理数据仓库未声明明确许可（2026-10-09）；代码许可不能自动套用到数据。</t>
         </is>
       </c>
     </row>
@@ -3821,7 +5809,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>旧报告已读全文；未核实可下载数据包和逐步过程文件。</t>
+          <t>旧报告已读全文；2026-10-09 再查论文和公开平台，仍未核实数据包。</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -3868,7 +5856,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>仅恢复旧检索题录和摘要线索；未取得数据样本。</t>
+          <t>已有题录与摘要；2026-10-09 核查全文中的资源链接和公开平台，仍未找到确认归属的数据包，未取得样本。</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -3900,12 +5888,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2606.04579v2</t>
+          <t>https://huggingface.co/datasets/InternScience/SCIPRM70K</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>旧检索摘要提出 SCIPRM70K 科学工具轨迹；未独立计数文件。</t>
+          <t>官方 GitHub 报告 17,818 条工具轨迹、86,314 个标注步骤；HF 发布 train.jsonl、test_search.jsonl、test_tool.jsonl，未独立计数。</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3915,7 +5903,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>仅恢复旧检索题录和摘要线索；未取得训练记录、标注说明或验证器。</t>
+          <t>2026-10-09 核到论文、官方 GitHub 与同组织 HF 数据文件目录；尚未全量核对记录、标注与验证器。</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -3925,12 +5913,12 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>过程奖励是否可靠、数据是否可得和是否泄露答案均需核验。</t>
+          <t>过程标签质量、奖励可靠性和答案泄漏仍需核验；可下载不代表可以直接作为科学正确性金标。</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 检索记录；arXiv:2606.04579v2；数据地址及许可待核。</t>
+          <t>HF 数据仓库暂无 README 或明确许可（2026-10-09）；数据可下载不等于条款已明确。</t>
         </is>
       </c>
     </row>
